--- a/低压盒/硬件电路接口.xlsx
+++ b/低压盒/硬件电路接口.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口表" sheetId="1" r:id="Rc79ada0b7ebf41fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校核清单" sheetId="2" r:id="Rc0373ab69fef4f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口表" sheetId="1" r:id="R273ff0e237ef4013"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校核清单" sheetId="2" r:id="R0fbaed1228b44502"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -515,7 +515,7 @@
       </x:c>
       <x:c r="J4" s="13"/>
     </x:row>
-    <x:row r="5" ht="85" customHeight="1">
+    <x:row r="5" ht="126" customHeight="1">
       <x:c r="A5" s="22" t="str">
         <x:v>BSPD</x:v>
       </x:c>
@@ -526,10 +526,13 @@
       </x:c>
       <x:c r="D5" s="23"/>
       <x:c r="E5" s="18" t="str">
-        <x:v>模拟量；板端阈值约 1.202 V
-故障/开路：低于阈值为电流条件无效
+        <x:v>传感器：0~50 A → 0~5 V
+目标电流：5 kW / 450 V = 11.11 A
+目标电压：5 × 11.11 / 50 ≈ 1.11 V
+故障/开路：低于目标阈值为电流条件无效
 对接：电流传感器
-备注：R25=31.6 kΩ、R26=10 kΩ；需用传感器曲线换算物理量</x:v>
+分压：R25/R26 = 34.8 kΩ/10 kΩ → 约 1.116 V
+备注：对应约 11.16 A / 5.02 kW；相对精确目标偏差约 +0.45%，电流阈值分压已修正</x:v>
       </x:c>
       <x:c r="F5" s="18"/>
       <x:c r="G5" s="23" t="str">
@@ -564,7 +567,7 @@
       <x:c r="I6" s="18"/>
       <x:c r="J6" s="18"/>
     </x:row>
-    <x:row r="7" ht="70" customHeight="1">
+    <x:row r="7" ht="126" customHeight="1">
       <x:c r="A7" s="22"/>
       <x:c r="B7" s="22"/>
       <x:c r="C7" s="23" t="str">
@@ -573,10 +576,13 @@
       </x:c>
       <x:c r="D7" s="23"/>
       <x:c r="E7" s="18" t="str">
-        <x:v>模拟量；板端阈值约 1.484 V
-故障/开路：低于阈值为制动条件无效
+        <x:v>传感器：0~20 MPa → 0~5 V
+目标油压：30 bar = 3 MPa
+目标电压：5 × 3 / 20 = 0.75 V
+故障/开路：低于目标阈值为制动条件无效
 对接：油压传感器4
-备注：H2 针脚顺序为 OIL4/OIL3/OIL2/OIL1</x:v>
+分压：R27/R28 = 5.62 kΩ/1 kΩ → 约 0.755 V（约 30.2 bar）
+备注：与 0.75 V 目标偏差约 +0.7%，油压阈值分压已修正</x:v>
       </x:c>
       <x:c r="F7" s="18"/>
       <x:c r="G7" s="23"/>
@@ -584,7 +590,7 @@
       <x:c r="I7" s="18"/>
       <x:c r="J7" s="18"/>
     </x:row>
-    <x:row r="8" ht="70" customHeight="1">
+    <x:row r="8" ht="126" customHeight="1">
       <x:c r="A8" s="22"/>
       <x:c r="B8" s="22"/>
       <x:c r="C8" s="23" t="str">
@@ -593,10 +599,13 @@
       </x:c>
       <x:c r="D8" s="23"/>
       <x:c r="E8" s="18" t="str">
-        <x:v>模拟量；板端阈值约 1.484 V
-故障/开路：同上
+        <x:v>传感器：0~20 MPa → 0~5 V
+目标油压：30 bar = 3 MPa
+目标电压：5 × 3 / 20 = 0.75 V
+故障/开路：低于目标阈值为制动条件无效
 对接：油压传感器3
-备注：R27=23.7 kΩ、R28=10 kΩ</x:v>
+分压：R27/R28 = 5.62 kΩ/1 kΩ → 约 0.755 V（约 30.2 bar）
+备注：与 0.75 V 目标偏差约 +0.7%，油压阈值分压已修正</x:v>
       </x:c>
       <x:c r="F8" s="18"/>
       <x:c r="G8" s="23"/>
@@ -604,7 +613,7 @@
       <x:c r="I8" s="18"/>
       <x:c r="J8" s="18"/>
     </x:row>
-    <x:row r="9" ht="70" customHeight="1">
+    <x:row r="9" ht="126" customHeight="1">
       <x:c r="A9" s="22"/>
       <x:c r="B9" s="22"/>
       <x:c r="C9" s="23" t="str">
@@ -613,10 +622,13 @@
       </x:c>
       <x:c r="D9" s="23"/>
       <x:c r="E9" s="18" t="str">
-        <x:v>模拟量；板端阈值约 1.484 V
-故障/开路：同上
+        <x:v>传感器：0~20 MPa → 0~5 V
+目标油压：30 bar = 3 MPa
+目标电压：5 × 3 / 20 = 0.75 V
+故障/开路：低于目标阈值为制动条件无效
 对接：油压传感器2
-备注：R27/R28 公共参考</x:v>
+分压：R27/R28 = 5.62 kΩ/1 kΩ → 约 0.755 V（约 30.2 bar）
+备注：与 0.75 V 目标偏差约 +0.7%，油压阈值分压已修正</x:v>
       </x:c>
       <x:c r="F9" s="18"/>
       <x:c r="G9" s="23"/>
@@ -624,7 +636,7 @@
       <x:c r="I9" s="18"/>
       <x:c r="J9" s="18"/>
     </x:row>
-    <x:row r="10" ht="70" customHeight="1">
+    <x:row r="10" ht="126" customHeight="1">
       <x:c r="A10" s="22"/>
       <x:c r="B10" s="22"/>
       <x:c r="C10" s="23" t="str">
@@ -633,10 +645,13 @@
       </x:c>
       <x:c r="D10" s="23"/>
       <x:c r="E10" s="18" t="str">
-        <x:v>模拟量；板端阈值约 1.484 V
-故障/开路：同上
+        <x:v>传感器：0~20 MPa → 0~5 V
+目标油压：30 bar = 3 MPa
+目标电压：5 × 3 / 20 = 0.75 V
+故障/开路：低于目标阈值为制动条件无效
 对接：油压传感器1
-备注：R27/R28 公共参考</x:v>
+分压：R27/R28 = 5.62 kΩ/1 kΩ → 约 0.755 V（约 30.2 bar）
+备注：与 0.75 V 目标偏差约 +0.7%，油压阈值分压已修正</x:v>
       </x:c>
       <x:c r="F10" s="18"/>
       <x:c r="G10" s="23"/>
@@ -1126,7 +1141,7 @@
       </x:c>
       <x:c r="J30" s="28"/>
     </x:row>
-    <x:row r="31" ht="70" customHeight="1">
+    <x:row r="31" ht="88" customHeight="1">
       <x:c r="A31" s="32"/>
       <x:c r="B31" s="32"/>
       <x:c r="C31" s="33" t="str">
@@ -1135,10 +1150,10 @@
       </x:c>
       <x:c r="D31" s="33"/>
       <x:c r="E31" s="28" t="str">
-        <x:v>0~5 V 检测节点
-故障/开路：开路由 100 kΩ 下拉为低
-对接：预充继电器检测
-备注：进入 RC 与施密特逻辑</x:v>
+        <x:v>辅助触点端 2；经 100 kΩ/100 nF 滤波进入逻辑
+与 PRE_1 分别连接同一预充辅助触点的两端
+触点断开时默认低；闭合时由 PRE_1 拉高
+禁止接继电器线圈端或外部有源电压</x:v>
       </x:c>
       <x:c r="F31" s="28"/>
       <x:c r="G31" s="33" t="str">
@@ -1154,7 +1169,7 @@
       </x:c>
       <x:c r="J31" s="28"/>
     </x:row>
-    <x:row r="32" ht="70" customHeight="1">
+    <x:row r="32" ht="88" customHeight="1">
       <x:c r="A32" s="32"/>
       <x:c r="B32" s="32"/>
       <x:c r="C32" s="33" t="str">
@@ -1163,10 +1178,10 @@
       </x:c>
       <x:c r="D32" s="33"/>
       <x:c r="E32" s="28" t="str">
-        <x:v>仅 4.7 kΩ 上拉
-故障/开路：未参与逻辑判定
-对接：预充线束
-备注：需确认用途或标 NC</x:v>
+        <x:v>辅助触点端 1；板内 4.7 kΩ 上拉至 5 V
+与 PRE_2 分别连接同一预充辅助触点的两端
+触点闭合时向 PRE_2 提供高电平
+禁止接继电器线圈端或外部有源电压</x:v>
       </x:c>
       <x:c r="F32" s="28"/>
       <x:c r="G32" s="33" t="str">
@@ -1182,7 +1197,7 @@
       </x:c>
       <x:c r="J32" s="28"/>
     </x:row>
-    <x:row r="33" ht="70" customHeight="1">
+    <x:row r="33" ht="88" customHeight="1">
       <x:c r="A33" s="32"/>
       <x:c r="B33" s="32"/>
       <x:c r="C33" s="33" t="str">
@@ -1191,10 +1206,10 @@
       </x:c>
       <x:c r="D33" s="33"/>
       <x:c r="E33" s="28" t="str">
-        <x:v>0~5 V 检测节点
-故障/开路：开路默认低
-对接：主负继电器检测
-备注：进入 RC 与施密特逻辑</x:v>
+        <x:v>辅助触点端 2；经 100 kΩ/100 nF 滤波进入逻辑
+与 MAINN_1 分别连接同一主负辅助触点的两端
+触点断开时默认低；闭合时由 MAINN_1 拉高
+禁止接继电器线圈端或外部有源电压</x:v>
       </x:c>
       <x:c r="F33" s="28"/>
       <x:c r="G33" s="33" t="str">
@@ -1210,7 +1225,7 @@
       </x:c>
       <x:c r="J33" s="28"/>
     </x:row>
-    <x:row r="34" ht="70" customHeight="1">
+    <x:row r="34" ht="88" customHeight="1">
       <x:c r="A34" s="32"/>
       <x:c r="B34" s="32"/>
       <x:c r="C34" s="33" t="str">
@@ -1219,10 +1234,10 @@
       </x:c>
       <x:c r="D34" s="33"/>
       <x:c r="E34" s="28" t="str">
-        <x:v>仅 4.7 kΩ 上拉
-故障/开路：未参与逻辑判定
-对接：主负线束
-备注：需确认用途或标 NC</x:v>
+        <x:v>辅助触点端 1；板内 4.7 kΩ 上拉至 5 V
+与 MAINN_2 分别连接同一主负辅助触点的两端
+触点闭合时向 MAINN_2 提供高电平
+禁止接继电器线圈端或外部有源电压</x:v>
       </x:c>
       <x:c r="F34" s="28"/>
       <x:c r="G34" s="33" t="str">
@@ -1238,7 +1253,7 @@
       </x:c>
       <x:c r="J34" s="28"/>
     </x:row>
-    <x:row r="35" ht="70" customHeight="1">
+    <x:row r="35" ht="88" customHeight="1">
       <x:c r="A35" s="32"/>
       <x:c r="B35" s="32"/>
       <x:c r="C35" s="33" t="str">
@@ -1247,10 +1262,10 @@
       </x:c>
       <x:c r="D35" s="33"/>
       <x:c r="E35" s="28" t="str">
-        <x:v>0~5 V 检测节点
-故障/开路：开路默认低
-对接：主正继电器检测
-备注：进入 RC 与施密特逻辑</x:v>
+        <x:v>辅助触点端 2；经 100 kΩ/100 nF 滤波进入逻辑
+与 MAINP_1 分别连接同一主正辅助触点的两端
+触点断开时默认低；闭合时由 MAINP_1 拉高
+禁止接继电器线圈端或外部有源电压</x:v>
       </x:c>
       <x:c r="F35" s="28"/>
       <x:c r="G35" s="33"/>
@@ -1258,7 +1273,7 @@
       <x:c r="I35" s="28"/>
       <x:c r="J35" s="28"/>
     </x:row>
-    <x:row r="36" ht="70" customHeight="1">
+    <x:row r="36" ht="88" customHeight="1">
       <x:c r="A36" s="32"/>
       <x:c r="B36" s="32"/>
       <x:c r="C36" s="33" t="str">
@@ -1267,10 +1282,10 @@
       </x:c>
       <x:c r="D36" s="33"/>
       <x:c r="E36" s="28" t="str">
-        <x:v>仅 4.7 kΩ 上拉
-故障/开路：未参与逻辑判定
-对接：主正线束
-备注：需确认用途或标 NC</x:v>
+        <x:v>辅助触点端 1；板内 4.7 kΩ 上拉至 5 V
+与 MAINP_2 分别连接同一主正辅助触点的两端
+触点闭合时向 MAINP_2 提供高电平
+禁止接继电器线圈端或外部有源电压</x:v>
       </x:c>
       <x:c r="F36" s="28"/>
       <x:c r="G36" s="33"/>
@@ -1828,24 +1843,24 @@
         <x:v>待系统确认</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="48" customHeight="1">
+    <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="42" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="B7" s="42" t="str">
         <x:v>继电器检测</x:v>
       </x:c>
       <x:c r="C7" s="42" t="str">
-        <x:v>三路 _1 未进入逻辑</x:v>
+        <x:v>三路 _1、_2 分别连接同一辅助触点的两端</x:v>
       </x:c>
       <x:c r="D7" s="42" t="str">
-        <x:v>MAINP_1/MAINN_1/PRE_1 只接 4.7 kΩ 上拉</x:v>
+        <x:v>*_1 由 4.7 kΩ 上拉；触点闭合后把 5 V 送到带 100 kΩ 下拉和 100 nF 滤波的 *_2</x:v>
       </x:c>
       <x:c r="E7" s="42" t="str">
-        <x:v>确认是 NC/预留还是遗漏的第二检测通道</x:v>
+        <x:v>线束按每只继电器一对无源辅助触点接线；禁止接线圈端或外部有源电压</x:v>
       </x:c>
       <x:c r="F7" s="42" t="str">
-        <x:v>待设计确认</x:v>
+        <x:v>已澄清</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -1868,24 +1883,24 @@
         <x:v>待设计确认</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="48" customHeight="1">
+    <x:row r="9" ht="76" customHeight="1">
       <x:c r="A9" s="42" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="B9" s="42" t="str">
         <x:v>BSPD</x:v>
       </x:c>
       <x:c r="C9" s="42" t="str">
-        <x:v>旧接口阈值与当前网表不一致</x:v>
+        <x:v>油压、电流阈值分压均已修正</x:v>
       </x:c>
       <x:c r="D9" s="42" t="str">
-        <x:v>旧表 0.75/1.11 V；网表计算 1.484/1.202 V</x:v>
+        <x:v>R27/R28 = 5.62 kΩ/1 kΩ → 约 0.755 V；R25/R26 = 34.8 kΩ/10 kΩ → 约 1.116 V。相对各自精确目标的偏差约为 +0.7% 和 +0.45%</x:v>
       </x:c>
       <x:c r="E9" s="42" t="str">
-        <x:v>已按当前网表校订，后续补传感器物理量标定</x:v>
+        <x:v>使用 0~5 V 可调信号实测油压约 0.75 V、电流约 1.11 V 的比较器翻转点，并记录元件容差和比较器失调影响</x:v>
       </x:c>
       <x:c r="F9" s="42" t="str">
-        <x:v>已校订</x:v>
+        <x:v>待台架确认</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">

--- a/低压盒/硬件电路接口.xlsx
+++ b/低压盒/硬件电路接口.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口表" sheetId="1" r:id="R273ff0e237ef4013"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校核清单" sheetId="2" r:id="R0fbaed1228b44502"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口表" sheetId="1" r:id="Ra5f604a906d64a26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校核清单" sheetId="2" r:id="Rfaf59c9e69d74755"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -480,7 +480,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>按原表左右分栏：每个信号单独列出；方向以当前板卡为观察点，VCU相关接口均按12 V定义。</x:v>
+        <x:v>按原表左右分栏；每个信号单独列出；方向以当前板卡为观察点。VCU_WDI例外：由VCU直接推挽输出0–5 V、10 Hz方波；其余VCU接口按各自定义。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -729,10 +729,10 @@
       </x:c>
       <x:c r="D14" s="33"/>
       <x:c r="E14" s="28" t="str">
-        <x:v>12 V PWM/看门狗脉冲
-故障/开路：停止翻转/异常时 WDO# 变低
-对接：VCU（12 V接口）
-备注：VCU相关均为12 V；当前UCC2946由5 V供电，需核对输入耐压与限流</x:v>
+        <x:v>0–5 V 推挽方波，10 Hz（VCU直接输出）
+故障/开路：停止翻转或频率异常时 WDO# 变低
+对接：VCU（5 V推挽输出）
+备注：VCU_WDI直接进入5 V供电的UCC2946，无需12 V→5 V转换；仍须核对输入高/低门限与频率窗口</x:v>
       </x:c>
       <x:c r="F14" s="28"/>
       <x:c r="G14" s="33" t="str">
@@ -828,7 +828,7 @@
         <x:v>0/12 V继电器状态反馈
 故障/开路：故障状态极性需台架确认
 对接：VCU（12 V接口）
-备注：VCU相关均为12 V；确认当前分压在全部触点组合下满足12 V逻辑门限</x:v>
+备注：本反馈按12 V接口校核，勿套用到5 V的VCU_WDI；确认当前分压在全部触点组合下满足12 V逻辑门限</x:v>
       </x:c>
       <x:c r="J17" s="28"/>
     </x:row>
@@ -1811,16 +1811,16 @@
         <x:v>EBS</x:v>
       </x:c>
       <x:c r="C5" s="42" t="str">
-        <x:v>VCU接口统一为12 V，当前前端兼容性需确认</x:v>
+        <x:v>VCU_WDI为5 V推挽10 Hz方波；其余VCU接口按各自电平定义</x:v>
       </x:c>
       <x:c r="D5" s="42" t="str">
-        <x:v>VCU_WDI/EBS_TRIG直达5 V供电IC；VCU_FB/EBS_CHECK由继电器反馈网络产生</x:v>
+        <x:v>VCU_WDI由VCU直接推挽输出并直达5 V供电UCC2946；EBS_TRIG仍为12 V并须调理；VCU_FB/EBS_CHECK由继电器反馈网络产生</x:v>
       </x:c>
       <x:c r="E5" s="42" t="str">
-        <x:v>核对12 V输入耐压与限流，并验证两路反馈的0/12 V门限、极性和源阻抗</x:v>
+        <x:v>验证VCU_WDI的0–5 V幅值、10 Hz频率和停止翻转故障动作；核对EBS_TRIG 12 V输入耐压与调理，并验证两路反馈的0/12 V门限、极性和源阻抗</x:v>
       </x:c>
       <x:c r="F5" s="42" t="str">
-        <x:v>待设计确认</x:v>
+        <x:v>待台架确认</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
